--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -2130,7 +2130,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187638</v>
+        <v>131187634</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>429004</v>
+        <v>428701</v>
       </c>
       <c r="R13" t="n">
-        <v>7064668</v>
+        <v>7064763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131187634</v>
+        <v>131187638</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428701</v>
+        <v>429004</v>
       </c>
       <c r="R14" t="n">
-        <v>7064763</v>
+        <v>7064668</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187639</v>
+        <v>131187637</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,16 +2948,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428867</v>
+        <v>428888</v>
       </c>
       <c r="R21" t="n">
-        <v>7064729</v>
+        <v>7064707</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187637</v>
+        <v>131187639</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428888</v>
+        <v>428867</v>
       </c>
       <c r="R22" t="n">
-        <v>7064707</v>
+        <v>7064729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187637</v>
+        <v>131187639</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,16 +2948,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428888</v>
+        <v>428867</v>
       </c>
       <c r="R21" t="n">
-        <v>7064707</v>
+        <v>7064729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187639</v>
+        <v>131187637</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428867</v>
+        <v>428888</v>
       </c>
       <c r="R22" t="n">
-        <v>7064729</v>
+        <v>7064707</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -948,7 +948,7 @@
         <v>131154647</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131154648</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131154646</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131154650</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>131154649</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187634</v>
+        <v>131187638</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428701</v>
+        <v>429004</v>
       </c>
       <c r="R13" t="n">
-        <v>7064763</v>
+        <v>7064668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131187638</v>
+        <v>131187634</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>429004</v>
+        <v>428701</v>
       </c>
       <c r="R14" t="n">
-        <v>7064668</v>
+        <v>7064763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131154647</v>
+        <v>131154640</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,26 +956,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +988,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428812</v>
+        <v>428785</v>
       </c>
       <c r="R4" t="n">
-        <v>7064738</v>
+        <v>7064733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,13 +1026,17 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1048,12 +1057,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131154640</v>
+        <v>131154647</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,31 +1091,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1114,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428785</v>
+        <v>428812</v>
       </c>
       <c r="R5" t="n">
-        <v>7064733</v>
+        <v>7064738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,17 +1156,13 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131187631</v>
+        <v>131187628</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428748</v>
+        <v>428842</v>
       </c>
       <c r="R23" t="n">
-        <v>7064756</v>
+        <v>7064682</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131187628</v>
+        <v>131187631</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428842</v>
+        <v>428748</v>
       </c>
       <c r="R24" t="n">
-        <v>7064682</v>
+        <v>7064756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131154640</v>
+        <v>131154647</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,31 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -988,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428785</v>
+        <v>428812</v>
       </c>
       <c r="R4" t="n">
-        <v>7064733</v>
+        <v>7064738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,17 +1021,13 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1057,12 +1048,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131154647</v>
+        <v>131154640</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,26 +1082,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1118,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428812</v>
+        <v>428785</v>
       </c>
       <c r="R5" t="n">
-        <v>7064738</v>
+        <v>7064733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,13 +1152,17 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
         <v>131154648</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131154646</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131154650</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,26 +1740,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R10" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,7 +1821,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1837,12 +1841,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1860,10 +1864,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,31 +1875,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1903,10 +1902,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R11" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1943,7 +1942,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,6 +1951,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187639</v>
+        <v>131187637</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,16 +2948,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428867</v>
+        <v>428888</v>
       </c>
       <c r="R21" t="n">
-        <v>7064729</v>
+        <v>7064707</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187637</v>
+        <v>131187639</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428888</v>
+        <v>428867</v>
       </c>
       <c r="R22" t="n">
-        <v>7064707</v>
+        <v>7064729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3141,7 +3141,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131187628</v>
+        <v>131187631</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428842</v>
+        <v>428748</v>
       </c>
       <c r="R23" t="n">
-        <v>7064682</v>
+        <v>7064756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131187631</v>
+        <v>131187628</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428748</v>
+        <v>428842</v>
       </c>
       <c r="R24" t="n">
-        <v>7064756</v>
+        <v>7064682</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,31 +1740,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R10" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1821,6 +1816,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1837,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1864,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,26 +1871,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1902,10 +1903,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R11" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1942,7 +1943,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,7 +1952,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154642</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154644</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154647</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>131154640</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131154648</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131154646</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131154650</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131154641</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,26 +1740,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R10" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,7 +1821,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1837,12 +1841,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1860,10 +1864,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,31 +1875,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1903,10 +1902,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R11" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1943,7 +1942,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,6 +1951,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
         <v>131154643</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>131187638</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131187634</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>131187636</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>131187632</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>131187629</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>131187630</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>131187635</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>131187637</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>131187639</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>131187631</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>131187628</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>131187633</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154642</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154644</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154647</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>131154640</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131154648</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131154646</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131154650</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131154641</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,31 +1740,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R10" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1821,6 +1816,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1837,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1864,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,26 +1871,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1902,10 +1903,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R11" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1942,7 +1943,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,7 +1952,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
         <v>131154643</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>131187638</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131187634</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>131187636</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>131187632</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>131187629</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>131187630</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>131187635</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187637</v>
+        <v>131187639</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,16 +2948,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428888</v>
+        <v>428867</v>
       </c>
       <c r="R21" t="n">
-        <v>7064707</v>
+        <v>7064729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187639</v>
+        <v>131187637</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428867</v>
+        <v>428888</v>
       </c>
       <c r="R22" t="n">
-        <v>7064729</v>
+        <v>7064707</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3144,7 +3144,7 @@
         <v>131187631</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>131187628</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>131187633</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131154647</v>
+        <v>131154640</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,26 +956,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +988,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428812</v>
+        <v>428785</v>
       </c>
       <c r="R4" t="n">
-        <v>7064738</v>
+        <v>7064733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,13 +1026,17 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1048,12 +1057,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131154640</v>
+        <v>131154647</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,31 +1091,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1114,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428785</v>
+        <v>428812</v>
       </c>
       <c r="R5" t="n">
-        <v>7064733</v>
+        <v>7064738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,17 +1156,13 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,26 +1740,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R10" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,7 +1821,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1837,12 +1841,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1860,10 +1864,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,31 +1875,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1903,10 +1902,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R11" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1943,7 +1942,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,6 +1951,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187639</v>
+        <v>131187637</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,16 +2948,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428867</v>
+        <v>428888</v>
       </c>
       <c r="R21" t="n">
-        <v>7064729</v>
+        <v>7064707</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187637</v>
+        <v>131187639</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428888</v>
+        <v>428867</v>
       </c>
       <c r="R22" t="n">
-        <v>7064707</v>
+        <v>7064729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,31 +1740,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R10" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1821,6 +1816,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1837,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1864,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,26 +1871,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1902,10 +1903,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R11" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1942,7 +1943,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,7 +1952,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154642</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154644</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154640</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131154647</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131154648</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131154646</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131154650</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131154641</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,26 +1740,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R10" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,7 +1821,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1837,12 +1841,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1860,10 +1864,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,31 +1875,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1903,10 +1902,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R11" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1943,7 +1942,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,6 +1951,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
         <v>131154643</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187638</v>
+        <v>131187634</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>429004</v>
+        <v>428701</v>
       </c>
       <c r="R13" t="n">
-        <v>7064668</v>
+        <v>7064763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131187634</v>
+        <v>131187638</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428701</v>
+        <v>429004</v>
       </c>
       <c r="R14" t="n">
-        <v>7064763</v>
+        <v>7064668</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>131187636</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>131187632</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>131187629</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>131187630</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>131187635</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187637</v>
+        <v>131187639</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,16 +2948,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428888</v>
+        <v>428867</v>
       </c>
       <c r="R21" t="n">
-        <v>7064707</v>
+        <v>7064729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187639</v>
+        <v>131187637</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428867</v>
+        <v>428888</v>
       </c>
       <c r="R22" t="n">
-        <v>7064729</v>
+        <v>7064707</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3144,7 +3144,7 @@
         <v>131187631</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>131187628</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>131187633</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131154640</v>
+        <v>131154647</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,31 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -988,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428785</v>
+        <v>428812</v>
       </c>
       <c r="R4" t="n">
-        <v>7064733</v>
+        <v>7064738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,17 +1021,13 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1057,12 +1048,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131154647</v>
+        <v>131154640</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,26 +1082,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1118,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428812</v>
+        <v>428785</v>
       </c>
       <c r="R5" t="n">
-        <v>7064738</v>
+        <v>7064733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,13 +1152,17 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,31 +1740,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R10" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1821,6 +1816,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1837,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1864,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,26 +1871,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1902,10 +1903,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R11" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1942,7 +1943,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,7 +1952,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187634</v>
+        <v>131187638</v>
       </c>
       <c r="B13" t="n">
         <v>57888</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428701</v>
+        <v>429004</v>
       </c>
       <c r="R13" t="n">
-        <v>7064763</v>
+        <v>7064668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131187638</v>
+        <v>131187634</v>
       </c>
       <c r="B14" t="n">
         <v>57888</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>429004</v>
+        <v>428701</v>
       </c>
       <c r="R14" t="n">
-        <v>7064668</v>
+        <v>7064763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -3141,7 +3141,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131187631</v>
+        <v>131187628</v>
       </c>
       <c r="B23" t="n">
         <v>57888</v>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428748</v>
+        <v>428842</v>
       </c>
       <c r="R23" t="n">
-        <v>7064756</v>
+        <v>7064682</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131187628</v>
+        <v>131187631</v>
       </c>
       <c r="B24" t="n">
         <v>57888</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428842</v>
+        <v>428748</v>
       </c>
       <c r="R24" t="n">
-        <v>7064682</v>
+        <v>7064756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154642</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154644</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154647</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>131154640</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131154648</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131154646</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131154650</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131154641</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>131154649</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>131154645</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>131154643</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>131187638</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131187634</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>131187636</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>131187632</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>131187629</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>131187630</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>131187635</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>131187639</v>
       </c>
       <c r="B21" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>131187637</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>131187628</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>131187631</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>131187633</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154642</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154644</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154647</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>131154640</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131154648</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131154646</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131154650</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131154641</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,26 +1740,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R10" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,7 +1821,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1837,12 +1841,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1860,10 +1864,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,31 +1875,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1903,10 +1902,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R11" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1943,7 +1942,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,6 +1951,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
         <v>131154643</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>131187638</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131187634</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>131187636</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>131187632</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187629</v>
+        <v>131187630</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428740</v>
+        <v>428747</v>
       </c>
       <c r="R18" t="n">
-        <v>7064730</v>
+        <v>7064740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187630</v>
+        <v>131187629</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428747</v>
+        <v>428740</v>
       </c>
       <c r="R19" t="n">
-        <v>7064740</v>
+        <v>7064730</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2838,7 +2838,7 @@
         <v>131187635</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>131187639</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>131187637</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131187628</v>
+        <v>131187631</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428842</v>
+        <v>428748</v>
       </c>
       <c r="R23" t="n">
-        <v>7064682</v>
+        <v>7064756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131187631</v>
+        <v>131187628</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428748</v>
+        <v>428842</v>
       </c>
       <c r="R24" t="n">
-        <v>7064756</v>
+        <v>7064682</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,7 +3348,7 @@
         <v>131187633</v>
       </c>
       <c r="B25" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154642</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154644</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154647</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>131154640</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131154648</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131154646</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>131154650</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>131154641</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154645</v>
+        <v>131154649</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,31 +1740,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428976</v>
+        <v>428953</v>
       </c>
       <c r="R10" t="n">
-        <v>7064670</v>
+        <v>7064677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1821,6 +1816,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1837,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1864,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154649</v>
+        <v>131154645</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,26 +1871,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1902,10 +1903,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428953</v>
+        <v>428976</v>
       </c>
       <c r="R11" t="n">
-        <v>7064677</v>
+        <v>7064670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1942,7 +1943,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,7 +1952,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
         <v>131154643</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>131187638</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131187634</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131187640</v>
       </c>
       <c r="B15" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>131187636</v>
       </c>
       <c r="B16" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>131187632</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187630</v>
+        <v>131187629</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428747</v>
+        <v>428740</v>
       </c>
       <c r="R18" t="n">
-        <v>7064740</v>
+        <v>7064730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187629</v>
+        <v>131187630</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428740</v>
+        <v>428747</v>
       </c>
       <c r="R19" t="n">
-        <v>7064730</v>
+        <v>7064740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2838,7 +2838,7 @@
         <v>131187635</v>
       </c>
       <c r="B20" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>131187639</v>
       </c>
       <c r="B21" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>131187637</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>131187631</v>
       </c>
       <c r="B23" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>131187628</v>
       </c>
       <c r="B24" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>131187633</v>
       </c>
       <c r="B25" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -2631,7 +2631,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187629</v>
+        <v>131187630</v>
       </c>
       <c r="B18" t="n">
         <v>57898</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428740</v>
+        <v>428747</v>
       </c>
       <c r="R18" t="n">
-        <v>7064730</v>
+        <v>7064740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,7 +2733,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187630</v>
+        <v>131187629</v>
       </c>
       <c r="B19" t="n">
         <v>57898</v>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428747</v>
+        <v>428740</v>
       </c>
       <c r="R19" t="n">
-        <v>7064740</v>
+        <v>7064730</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187639</v>
+        <v>131187637</v>
       </c>
       <c r="B21" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,16 +2948,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428867</v>
+        <v>428888</v>
       </c>
       <c r="R21" t="n">
-        <v>7064729</v>
+        <v>7064707</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187637</v>
+        <v>131187639</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428888</v>
+        <v>428867</v>
       </c>
       <c r="R22" t="n">
-        <v>7064707</v>
+        <v>7064729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131154642</v>
+        <v>131154646</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428914</v>
+        <v>428791</v>
       </c>
       <c r="R2" t="n">
-        <v>7064718</v>
+        <v>7064695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en naturhänsyn-snitslad stående död gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,12 +783,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,42 +806,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131154644</v>
+        <v>131154647</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428957</v>
+        <v>428812</v>
       </c>
       <c r="R3" t="n">
-        <v>7064698</v>
+        <v>7064738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,17 +882,13 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,12 +909,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,14 +932,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131154647</v>
+        <v>131154648</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -983,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428812</v>
+        <v>428902</v>
       </c>
       <c r="R4" t="n">
-        <v>7064738</v>
+        <v>7064728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,6 +1006,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,42 +1063,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131154640</v>
+        <v>131154649</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1114,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428785</v>
+        <v>428953</v>
       </c>
       <c r="R5" t="n">
-        <v>7064733</v>
+        <v>7064677</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1141,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,6 +1150,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1183,12 +1171,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1206,14 +1194,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131154648</v>
+        <v>131154650</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1244,10 +1232,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428902</v>
+        <v>428961</v>
       </c>
       <c r="R6" t="n">
-        <v>7064728</v>
+        <v>7064697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,11 +1268,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1337,48 +1320,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131154646</v>
+        <v>131187639</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjöflon, Jmt</t>
+          <t>Höjdsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428791</v>
+        <v>428867</v>
       </c>
       <c r="R7" t="n">
-        <v>7064695</v>
+        <v>7064729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,7 +1395,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,54 +1404,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131154650</v>
+        <v>131154640</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,26 +1433,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1506,10 +1465,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428961</v>
+        <v>428785</v>
       </c>
       <c r="R8" t="n">
-        <v>7064697</v>
+        <v>7064733</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,13 +1503,17 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1571,12 +1534,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1597,7 +1560,7 @@
         <v>131154641</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1729,10 +1692,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154649</v>
+        <v>131154642</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,26 +1703,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1767,10 +1735,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428953</v>
+        <v>428914</v>
       </c>
       <c r="R10" t="n">
-        <v>7064677</v>
+        <v>7064718</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1807,7 +1775,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på en naturhänsyn-snitslad stående död gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,7 +1784,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1837,12 +1804,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1860,10 +1827,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154645</v>
+        <v>131154643</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1860,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1903,10 +1870,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428976</v>
+        <v>428933</v>
       </c>
       <c r="R11" t="n">
-        <v>7064670</v>
+        <v>7064703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1943,7 +1910,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,12 +1939,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1995,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131154643</v>
+        <v>131154644</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2028,7 +1995,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2038,10 +2005,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>428933</v>
+        <v>428957</v>
       </c>
       <c r="R12" t="n">
-        <v>7064703</v>
+        <v>7064698</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2078,7 +2045,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gammal gran.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en stående död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2107,12 +2074,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2130,10 +2097,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187638</v>
+        <v>131154645</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,16 +2126,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Höjdsjön, Jmt</t>
+          <t>Sjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>429004</v>
+        <v>428976</v>
       </c>
       <c r="R13" t="n">
-        <v>7064668</v>
+        <v>7064670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2205,7 +2180,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gammal grovbarkad gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2216,26 +2191,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131187634</v>
+        <v>131187628</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428701</v>
+        <v>428842</v>
       </c>
       <c r="R14" t="n">
-        <v>7064763</v>
+        <v>7064682</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2334,10 +2334,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187640</v>
+        <v>131187629</v>
       </c>
       <c r="B15" t="n">
-        <v>91848</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,19 +2345,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2365,10 +2369,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>429004</v>
+        <v>428740</v>
       </c>
       <c r="R15" t="n">
-        <v>7064639</v>
+        <v>7064730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2401,6 +2405,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2427,10 +2436,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187636</v>
+        <v>131187630</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,10 +2471,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428864</v>
+        <v>428747</v>
       </c>
       <c r="R16" t="n">
-        <v>7064680</v>
+        <v>7064740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2502,7 +2511,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2529,10 +2538,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187632</v>
+        <v>131187631</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2564,10 +2573,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428742</v>
+        <v>428748</v>
       </c>
       <c r="R17" t="n">
-        <v>7064758</v>
+        <v>7064756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2631,10 +2640,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187630</v>
+        <v>131187632</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,10 +2675,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428747</v>
+        <v>428742</v>
       </c>
       <c r="R18" t="n">
-        <v>7064740</v>
+        <v>7064758</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2706,7 +2715,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187629</v>
+        <v>131187633</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2768,10 +2777,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428740</v>
+        <v>428705</v>
       </c>
       <c r="R19" t="n">
-        <v>7064730</v>
+        <v>7064756</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2835,10 +2844,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187635</v>
+        <v>131187634</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,10 +2879,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428858</v>
+        <v>428701</v>
       </c>
       <c r="R20" t="n">
-        <v>7064677</v>
+        <v>7064763</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187637</v>
+        <v>131187635</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,10 +2981,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428888</v>
+        <v>428858</v>
       </c>
       <c r="R21" t="n">
-        <v>7064707</v>
+        <v>7064677</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3039,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187639</v>
+        <v>131187636</v>
       </c>
       <c r="B22" t="n">
-        <v>57895</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,16 +3059,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3074,10 +3083,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428867</v>
+        <v>428864</v>
       </c>
       <c r="R22" t="n">
-        <v>7064729</v>
+        <v>7064680</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3123,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3141,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131187631</v>
+        <v>131187637</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,10 +3185,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428748</v>
+        <v>428888</v>
       </c>
       <c r="R23" t="n">
-        <v>7064756</v>
+        <v>7064707</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3243,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131187628</v>
+        <v>131187638</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,10 +3287,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428842</v>
+        <v>429004</v>
       </c>
       <c r="R24" t="n">
-        <v>7064682</v>
+        <v>7064668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,7 +3327,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3342,108 +3351,6 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>131187633</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57898</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Höjdsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>428705</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7064756</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61399-2025 artfynd.xlsx
+++ b/artfynd/A 61399-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154646</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,6 +939,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154647</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1060,6 +1075,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154648</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1191,6 +1211,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154649</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154650</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1419,6 +1449,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187639</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1554,6 +1589,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154640</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1689,6 +1729,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154641</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1824,6 +1869,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154642</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1959,6 +2009,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154643</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2094,6 +2149,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154644</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2229,6 +2289,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154645</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2331,6 +2396,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187628</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2433,6 +2503,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187629</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2535,6 +2610,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187630</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2637,6 +2717,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187631</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2739,6 +2824,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187632</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2841,6 +2931,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187633</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2943,6 +3038,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187634</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3045,6 +3145,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187635</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3147,6 +3252,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187636</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3249,6 +3359,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187637</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3351,8 +3466,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187638</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>